--- a/nr-update-patient/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/nr-update-patient/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T08:27:16+00:00</t>
+    <t>2025-10-21T13:57:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-patient/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/nr-update-patient/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T13:57:20+00:00</t>
+    <t>2025-10-21T14:02:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
